--- a/projects/ecm-compute/v1.0.0/export/用户组管理/用户组管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户组管理/用户组管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -604,6 +604,50 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>e_name_name</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>${gen_test_name('name')}</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>步骤 创建用户组 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>e_mutable_description</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>${gen_mutable_value()}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>步骤 创建用户组 的可变字段</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects/ecm-compute/v1.0.0/export/用户组管理/用户组管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户组管理/用户组管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_entity_0_id</t>
+          <t>e_entity_list_0_tenantId</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>${entity_0_id}</t>
+          <t>${entity_list_0_tenantId}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>由 前置 API: display-by-role 提取 (path: entity[0].id)</t>
+          <t>由 获取用户列表 提取 (path: entity.list[0].tenantId)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_name_name</t>
+          <t>e_entity_0_userId</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,32 +617,54 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>${gen_test_name('name')}</t>
+          <t>${entity_0_userId}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>步骤 创建用户组 的名称字段</t>
+          <t>由 前置 API: access-log 提取 (path: entity[0].userId)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>e_name_name</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>${gen_test_name('name')}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>步骤 创建用户组 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>e_mutable_description</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>${gen_mutable_value()}</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>步骤 创建用户组 的可变字段</t>
         </is>

--- a/projects/ecm-compute/v1.0.0/export/用户组管理/用户组管理_params.xlsx
+++ b/projects/ecm-compute/v1.0.0/export/用户组管理/用户组管理_params.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_entity_0_userId</t>
+          <t>e_entity_list_0_id</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>${entity_0_userId}</t>
+          <t>${entity_list_0_id}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>由 前置 API: access-log 提取 (path: entity[0].userId)</t>
+          <t>由 获取用户列表 提取 (path: entity.list[0].id)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_name_name</t>
+          <t>e_entity_list_0_policyList_0_id</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -639,32 +639,54 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>${gen_test_name('name')}</t>
+          <t>${entity_list_0_policyList_0_id}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>步骤 创建用户组 的名称字段</t>
+          <t>由 获取用户列表 提取 (path: entity.list[0].policyList[0].id)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>e_name_name</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>${gen_test_name('name')}</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>步骤 创建用户组 的名称字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>e_mutable_description</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>${gen_mutable_value()}</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>步骤 创建用户组 的可变字段</t>
         </is>
